--- a/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
+++ b/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="리워드구성" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정물량" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스토리페이지섹션" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,4 +804,122 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20250308-wadiz-journal-rewards-earlybird-story</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:23:21.073+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S08:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>원가·마진·생산능력·배송·AI 기능·개인정보 처리 및 규제 검토를 후속 검증 조건으로 두고, 리워드·얼리버드·스토리 페이지 기획 방향과 관련 산출물 업데이트를 승인한다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AI driven journal recorder 와디즈 런칭을 위한 리워드 구성, 얼리버드 운영안, 스토리 페이지 구조 확정 및 관련 산출물 업데이트</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>와디즈 캠페인 기획서; 리워드 구성안; 얼리버드 운영안; 와디즈 스토리 페이지 기획서</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/c128698c6376c118643d312a5ee69f7ed40832ad</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
+++ b/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
@@ -812,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,56 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20250308-wadiz-approval-deliverable-gates</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:26:40.846+09:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S08:B10000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>리워드·얼리버드·스토리 페이지 및 관련 문서 산출물의 업데이트를 승인한다. 단, 가격·수량·일정·대외 공개 문구는 원가·마진·생산·배송·AI 기능·개인정보·규제 검증과 담당자·증빙·승인 게이트 확인 후 최종 확정한다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AI driven journal recorder의 와디즈 런칭 범위와 리워드·얼리버드·스토리 페이지 확정 방향 및 검증 조건을 관련 산출물에 연결해 기록</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>와디즈 캠페인 기획서; 리워드 구성안; 얼리버드 운영안; 와디즈 스토리 페이지 기획서; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/5f4aad96fd8e6dfb56a5b9c7614a1c90660b21db</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
+++ b/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
@@ -812,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,6 +969,56 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20250308-wadiz-launch-approval-gates</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:31:33.221+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S08:B01000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>승인(bench auto)을 런칭 요건 반영 승인 상태로 기록한다. 오픈예정 알림신청 2주, 본 펀딩 4주, 시제품 검수 완료 목표를 본 펀딩 오픈 10일 전으로 반영하며, 리워드 구성·얼리버드 물량·스토리 페이지 구조는 담당 의사결정권자와 확정 기한 확인 전까지 미확정 상태로 유지한다. DA는 조건부 승인으로 낮추고 의사결정권자·기한·의존성·컴플라이언스 게이트·검수 합격 기준 및 실패 대응을 확정할 것을 권고했다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AI driven journal recorder의 와디즈 런칭 요건 반영 승인, 일정 및 시제품 검수 목표 확정, 리워드·얼리버드·스토리 구조 담당자 확정 대기</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>와디즈 런칭 기획서; 와디즈 스토리 페이지 기획서; 런칭 일정 및 검수 계획; 요구사항 추적표</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/5bc1f0b905b71799ed19bb7075ff63a48c8f8c4e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
+++ b/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
@@ -812,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,6 +1019,56 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20250308-wadiz-approval-execution</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:35:23.095+09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S08:B00100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>와디즈 런칭 방향과 영향 산출물 갱신 범위는 승인 및 기록하되, 리워드 가격·수량·얼리버드 총량·스토리 문구·최종 일정은 원가·생산·개인정보·규제 검증과 담당자·증빙·승인 게이트 확인 후 확정한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AI driven journal recorder의 와디즈 런칭 준비 범위, 리워드 구성, 얼리버드 운영, 스토리 페이지 구조, 런칭 일정 및 검증 게이트를 관련 산출물에 연결한다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>와디즈 캠페인 기획서; 리워드 구성안; 얼리버드 운영안; 와디즈 스토리 페이지 기획서; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/caa1e01e5cd2ec3e0b18006bdc71b5d558c76113</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
+++ b/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
@@ -812,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1069,6 +1069,56 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20250308-wadiz-approved-deliverables</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:39:23.288+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S08:B00010</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>산출물 변경을 승인하고 반영 완료로 기록한다. 단, 리워드 가격·수량·얼리버드 총량·최종 스토리 문구·확정 일정은 재무·재고·개인정보·규제 검증과 의사결정권자 승인 전까지 미확정으로 유지한다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>와디즈 런칭의 리워드·얼리버드·스토리 구조와 일정·검증 게이트를 관련 산출물에 반영하고 미결정 항목을 추적한다.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>와디즈 캠페인 기획서; 리워드 구성안; 얼리버드 운영안; 와디즈 스토리 페이지 기획서; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/dbf681cb3e7bd78039e3fca640b613a468f1747c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
+++ b/scenarios/S08_wadiz_product_launch/deliverables/리워드구성_일정물량_시트.xlsx
@@ -812,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,6 +1119,56 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20250308-wadiz-approval-execution-record</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:42:56.589+09:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bench:S08:B00001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7개 산출물의 변경 및 문서엔진 갱신 완료를 승인 기록으로 남기되, 가격·수량·최종 문구·공개 사양·일정은 책임자 승인과 재무·재고·개인정보·규제·시제품 검증 완료 전까지 미확정으로 유지한다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>와디즈 런칭 관련 7개 산출물의 구성·검증 기준을 반영하고 미확정 의사결정과 리스크를 추적한다.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>와디즈 캠페인 기획서; 리워드 구성안; 얼리버드 운영안; 와디즈 스토리 페이지 기획서; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/8ce2c6130969d8a5398f784fe526bede6b317504</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
